--- a/hanzicraft_9000.xlsx
+++ b/hanzicraft_9000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1501"/>
+  <dimension ref="A1:C2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22933,6 +22933,7506 @@
         </is>
       </c>
     </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>骗</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%AA%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>凤</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>慧</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%85%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>媒</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AA%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>佩</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>愤</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%84%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>扑</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>龄</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%BE%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>驱</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A9%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>惜</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>豪</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B1%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>掩</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8E%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>兼</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>跃</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B7%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>尸</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>肃</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>帕</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>驶</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A9%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>堡</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A0%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>届</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>欣</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AC%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>惠</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>册</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>储</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%82%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A3%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>桑</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A1%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>闲</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%97%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>惨</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>洁</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B4%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>踪</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B8%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>勃</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8B%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>宾</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>频</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="n">
+        <v>1534</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>仇</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>磨</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A3%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>递</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>邪</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>撞</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%92%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>拟</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>滚</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BB%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>奏</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>巡</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B7%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="n">
+        <v>1543</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>颜</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>剂</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%89%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>绩</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="n">
+        <v>1546</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>贡</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>疯</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%96%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>坡</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9D%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>瞧</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9E%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>截</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>燃</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%87%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="n">
+        <v>1552</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>焦</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%84%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>殿</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AE%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="n">
+        <v>1554</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>伪</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>柳</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="n">
+        <v>1556</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>锁</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%94%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>逼</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>颇</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="n">
+        <v>1559</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>昏</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="n">
+        <v>1560</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>劝</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>呈</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="n">
+        <v>1562</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>搜</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%90%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>勤</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8B%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>戒</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>驾</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A9%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="n">
+        <v>1566</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>漂</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BC%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="n">
+        <v>1567</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>饮</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A5%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9B%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>朵</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="n">
+        <v>1570</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>仔</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>柔</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>俩</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BF%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>孟</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AD%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>腐</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%85%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>幼</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>1576</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>践</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B7%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>籍</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B1%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>牧</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>凉</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>牲</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>佳</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>娜</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A8%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>浓</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>芳</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8A%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>稿</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A8%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>竹</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AB%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>1587</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>腹</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%85%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B7%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>逻</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>垂</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9E%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>遵</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%81%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>脉</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%84%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>貌</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B2%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>1594</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>柏</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>狱</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8B%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>猜</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8C%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>怜</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>1598</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>惑</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>陶</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>兽</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>帐</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>饰</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A5%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>昌</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>叙</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>躺</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BA%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>钢</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%92%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>沟</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B2%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>寄</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>扶</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>铺</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%93%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>邓</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>寿</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>1614</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>惧</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>询</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="n">
+        <v>1616</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>汤</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B1%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="n">
+        <v>1617</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>盗</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="n">
+        <v>1618</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>肥</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>尝</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>匆</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="n">
+        <v>1621</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>辉</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>奈</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>扣</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>廷</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BB%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>澳</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BE%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>嘛</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%98%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>董</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%91%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>迁</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>凝</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>慰</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%85%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>厌</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8E%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>脏</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%84%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>腾</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%85%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>幽</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>怨</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>鞋</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9E%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>丢</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>埋</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9F%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>泉</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B3%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>涌</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B6%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>辖</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>躲</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BA%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>晋</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%99%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B4%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>艰</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%89%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%AD%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>吾</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>慌</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%85%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>祝</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A5%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>邮</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>吐</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>狠</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8B%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>鉴</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%89%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>曰</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9B%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>械</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A2%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>咬</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%92%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>邻</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>挤</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>弯</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>椅</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A4%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>陪</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="n">
+        <v>1663</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>割</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%89%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="n">
+        <v>1664</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>揭</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8F%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>韦</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9F%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>悟</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%82%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="n">
+        <v>1667</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>聪</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%81%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="n">
+        <v>1668</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>雾</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9B%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>锋</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%94%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="n">
+        <v>1670</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>梯</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A2%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>猫</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8C%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>祥</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A5%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>阔</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%98%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>誉</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AA%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="n">
+        <v>1675</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>筹</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AD%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="n">
+        <v>1676</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>丛</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>牵</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>鸣</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%B8%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>沈</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B2%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>阁</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%98%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>穆</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A9%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>屈</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>旨</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%97%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>袖</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A2%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>猎</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8C%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>臂</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%87%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>蛇</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%9B%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>贺</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>柱</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>抛</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>鼠</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%BC%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>瑟</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%91%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>戈</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>牢</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="n">
+        <v>1695</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>逊</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="n">
+        <v>1696</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>迈</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>欺</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AC%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="n">
+        <v>1698</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>吨</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="n">
+        <v>1699</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>琴</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%90%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>衰</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A1%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>瓶</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%93%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>恼</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%81%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>燕</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%87%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>仲</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>诱</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>狼</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8B%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>池</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B1%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>疼</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%96%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>卢</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="n">
+        <v>1710</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>仗</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="n">
+        <v>1711</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>冠</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="n">
+        <v>1712</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>粒</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B2%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>遥</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%81%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>吕</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>玄</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8E%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>尘</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>冯</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>抚</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>浅</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>敦</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%95%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>纠</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>钻</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%92%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>晶</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%99%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>岂</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B2%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="n">
+        <v>1725</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>峡</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B3%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="n">
+        <v>1726</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>苍</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8B%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="n">
+        <v>1727</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>喷</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%96%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="n">
+        <v>1728</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>耗</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="n">
+        <v>1729</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>凌</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="n">
+        <v>1730</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>敲</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%95%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="n">
+        <v>1731</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>菌</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8F%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="n">
+        <v>1732</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>赔</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="n">
+        <v>1733</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>涂</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B6%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="n">
+        <v>1734</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>粹</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B2%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="n">
+        <v>1735</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>扁</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="n">
+        <v>1736</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>亏</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="n">
+        <v>1737</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>寂</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="n">
+        <v>1738</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>煤</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%85%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="n">
+        <v>1739</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>熊</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%86%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="n">
+        <v>1740</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>恭</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%81%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="n">
+        <v>1741</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>湿</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B9%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>循</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BE%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="n">
+        <v>1743</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>暖</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9A%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="n">
+        <v>1744</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>糖</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B3%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>赋</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>抑</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>秩</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A7%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>帽</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>哀</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%93%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>宿</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>踏</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B8%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="n">
+        <v>1752</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>烂</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%83%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="n">
+        <v>1753</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>袁</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A2%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="n">
+        <v>1754</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>侯</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BE%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="n">
+        <v>1755</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>抖</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="n">
+        <v>1756</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>夹</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="n">
+        <v>1757</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>昆</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="n">
+        <v>1758</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>肝</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="n">
+        <v>1759</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>擦</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%93%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>猪</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8C%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>炼</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%82%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="n">
+        <v>1762</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>恒</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%81%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="n">
+        <v>1763</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>慎</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%85%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="n">
+        <v>1764</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>搬</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%90%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>纽</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="n">
+        <v>1766</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>纹</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>玻</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8E%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="n">
+        <v>1768</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>渔</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B8%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>磁</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A3%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="n">
+        <v>1770</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%93%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>齿</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%BD%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="n">
+        <v>1772</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>跨</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B7%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>押</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="n">
+        <v>1774</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>怖</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="n">
+        <v>1775</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>漠</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BC%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="n">
+        <v>1776</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>疲</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%96%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>叛</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>遣</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%81%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="n">
+        <v>1779</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>兹</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>祭</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A5%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>醉</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%86%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="n">
+        <v>1782</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>拳</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="n">
+        <v>1783</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>弥</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="n">
+        <v>1784</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>斜</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>档</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A1%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="n">
+        <v>1786</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>稀</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A8%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="n">
+        <v>1787</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>捷</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8D%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="n">
+        <v>1788</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>肤</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>疫</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%96%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="n">
+        <v>1790</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>肿</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="n">
+        <v>1791</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>豆</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B1%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="n">
+        <v>1792</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>削</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%89%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>岗</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B2%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="n">
+        <v>1794</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>晃</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%99%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="n">
+        <v>1795</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>吞</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="n">
+        <v>1796</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>宏</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>癌</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%99%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>肚</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="n">
+        <v>1799</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>隶</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9A%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>履</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B6%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>耀</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>扭</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>坛</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9D%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>拨</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>沃</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B2%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>绘</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>伐</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>堪</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A0%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>仆</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>郭</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%83%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>牺</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>歼</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="n">
+        <v>1814</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>墓</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A2%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="n">
+        <v>1815</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>雇</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9B%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="n">
+        <v>1816</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>廉</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BB%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>契</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="n">
+        <v>1818</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>拼</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="n">
+        <v>1819</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>惩</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>捉</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8D%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>刷</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="n">
+        <v>1822</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>劫</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="n">
+        <v>1823</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>嫌</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AB%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>瓜</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%93%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>歇</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="n">
+        <v>1826</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>雕</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9B%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="n">
+        <v>1827</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>闷</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%97%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>乳</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>串</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="n">
+        <v>1830</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>娃</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A8%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="n">
+        <v>1831</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>缴</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BC%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="n">
+        <v>1832</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>唤</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%94%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>赢</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="n">
+        <v>1834</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>莲</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8E%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>霸</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9C%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="n">
+        <v>1836</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>桃</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A1%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>妥</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A6%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>瘦</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%98%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="n">
+        <v>1839</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>搭</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%90%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>赴</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="n">
+        <v>1841</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>岳</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B2%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="n">
+        <v>1842</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>嘉</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%98%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="n">
+        <v>1843</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>舱</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%88%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="n">
+        <v>1844</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>俊</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BF%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>址</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9D%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>庞</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BA%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="n">
+        <v>1847</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>耕</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="n">
+        <v>1848</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>锐</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%94%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="n">
+        <v>1849</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>缝</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BC%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>悔</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%82%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="n">
+        <v>1851</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>邀</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="n">
+        <v>1852</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>玲</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8E%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>惟</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="n">
+        <v>1854</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>斥</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="n">
+        <v>1855</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>宅</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="n">
+        <v>1856</v>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>添</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B7%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="n">
+        <v>1857</v>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>挖</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="n">
+        <v>1858</v>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>呵</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>讼</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="n">
+        <v>1860</v>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B0%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>浩</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="n">
+        <v>1862</v>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BE%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>斤</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="n">
+        <v>1864</v>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>酷</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%85%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="n">
+        <v>1865</v>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>掠</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8E%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="n">
+        <v>1866</v>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>妖</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A6%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="n">
+        <v>1867</v>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>祸</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A5%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="n">
+        <v>1868</v>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>侍</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BE%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="n">
+        <v>1869</v>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>妨</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A6%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>贪</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>挣</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="n">
+        <v>1873</v>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>汪</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B1%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="n">
+        <v>1874</v>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>尿</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>莉</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8E%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="n">
+        <v>1876</v>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>悬</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%82%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="n">
+        <v>1877</v>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>唇</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%94%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>翰</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BF%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>仓</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>轨</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BD%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="n">
+        <v>1881</v>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>枚</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9E%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>盐</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>览</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>傅</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%82%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>帅</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="n">
+        <v>1886</v>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>庙</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BA%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="n">
+        <v>1887</v>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>芬</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8A%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="n">
+        <v>1888</v>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>屏</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>寺</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="n">
+        <v>1890</v>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>胖</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%83%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>璃</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%92%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>愚</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%84%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>滴</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BB%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>疏</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%96%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>萧</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%90%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>姿</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A7%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="n">
+        <v>1897</v>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>颤</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>丑</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>劣</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>柯</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>寸</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>扔</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>盯</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>辱</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>匹</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>俱</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BF%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>辨</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>饿</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A5%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>蜂</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%9C%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>哦</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%93%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>腔</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%85%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>郁</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%83%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>溃</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BA%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>谨</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B0%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="n">
+        <v>1915</v>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>糟</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B3%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>葛</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%91%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="n">
+        <v>1917</v>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>苗</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8B%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="n">
+        <v>1918</v>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>肠</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="n">
+        <v>1919</v>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>忌</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BF%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>溜</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BA%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="n">
+        <v>1921</v>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>鸿</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%B8%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>爵</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%88%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>鹏</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%B9%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>鹰</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%B9%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>笼</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AC%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>丘</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="n">
+        <v>1927</v>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>桂</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A1%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>滋</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BB%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>聊</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%81%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>挡</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>纲</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="n">
+        <v>1932</v>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>肌</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%82%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>茨</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8C%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>壳</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A3%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>痕</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%97%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>碗</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A2%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>穴</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A9%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>膀</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%86%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="n">
+        <v>1939</v>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>贤</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>卧</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>膜</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%86%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>毅</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AF%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>锦</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%94%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="n">
+        <v>1945</v>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>欠</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AC%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="n">
+        <v>1946</v>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>哩</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%93%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>函</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>茫</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8C%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>昂</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>薛</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%96%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>皱</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9A%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>夸</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>豫</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B1%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>胃</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%83%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>舌</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%88%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>剥</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%89%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>傲</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%82%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>拾</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>窝</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AA%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>睁</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9D%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>携</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%90%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>陵</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>哼</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%93%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>棉</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A3%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%99%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>铃</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%93%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>填</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A1%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>饲</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A5%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>渴</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B8%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>吻</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>扮</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>逆</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>脆</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%84%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>喘</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%96%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>罩</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BD%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>卜</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>炉</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%82%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>柴</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>愉</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%84%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>绳</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>胎</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%83%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>蓄</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%93%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>眠</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9C%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>竭</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AB%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>喂</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%96%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>傻</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%82%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>慕</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%85%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>浑</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>奸</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>扇</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>柜</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>悦</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%82%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>拦</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>诞</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>饱</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A5%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>乾</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>泡</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B3%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>贼</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>亭</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>夕</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
